--- a/file/events.xlsx
+++ b/file/events.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Downloads\test\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Braga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A937887B-DA05-4E20-841C-254745649114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7804F05-1332-4CBC-A94F-0FEC480D461D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="225" yWindow="1980" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$94</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,9 +51,6 @@
     <t>OlyBet Baltics Cup (y)</t>
   </si>
   <si>
-    <t>Hellcase Cup (n)</t>
-  </si>
-  <si>
     <t>Icelandic Esports League Season (n)</t>
   </si>
   <si>
@@ -87,9 +87,6 @@
     <t>MistGames Nordic Championship (y)</t>
   </si>
   <si>
-    <t>BtcTurk GameFest (y)</t>
-  </si>
-  <si>
     <t>Whale Cup (y)</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
     <t>FiReLEAGUE Buenos Aires (y)</t>
   </si>
   <si>
-    <t>GameBox Festival (y)</t>
-  </si>
-  <si>
     <t>Nitro Fresh Masters (y)</t>
   </si>
   <si>
@@ -195,18 +189,12 @@
     <t>1xBet Contest Pro League Season (n)</t>
   </si>
   <si>
-    <t>Svenska CS-Ligan (y)</t>
-  </si>
-  <si>
     <t>Master League Portugal (n)</t>
   </si>
   <si>
     <t>OMEN Retake Season (n)</t>
   </si>
   <si>
-    <t>Winamax Spanish Cirtuit (y)</t>
-  </si>
-  <si>
     <t>United21 League Season (n)</t>
   </si>
   <si>
@@ -255,27 +243,15 @@
     <t>BLAST Rising (continent) (y) Season (n)</t>
   </si>
   <si>
-    <t>ACE (continent) Masters (y) Season (n)</t>
-  </si>
-  <si>
-    <t>AMD GameOn (y)</t>
-  </si>
-  <si>
     <t>CCT Season (n) (continent) Series (n)</t>
   </si>
   <si>
     <t>FISSURE Playground (n)</t>
   </si>
   <si>
-    <t>BetBoom Battle Season (n)</t>
-  </si>
-  <si>
     <t>IEM Challenger League Season (n) (continent)</t>
   </si>
   <si>
-    <t>ZOWIE eXTREMESLAND Asia (y)</t>
-  </si>
-  <si>
     <t>ESEA Advanced Season (n) (continent)</t>
   </si>
   <si>
@@ -285,12 +261,6 @@
     <t>Exort Series (n)</t>
   </si>
   <si>
-    <t>CBCS Masters (y)</t>
-  </si>
-  <si>
-    <t>PXB Masters (y)</t>
-  </si>
-  <si>
     <t>BLAST Premier (y) Event</t>
   </si>
   <si>
@@ -328,16 +298,62 @@
   </si>
   <si>
     <t>last date</t>
+  </si>
+  <si>
+    <t>BLAST Open (country) (y)</t>
+  </si>
+  <si>
+    <t>BLAST Pro Series (country) (year)</t>
+  </si>
+  <si>
+    <t>BLAST Rivals (y) season (n)</t>
+  </si>
+  <si>
+    <t>CS Asia Champions (y)</t>
+  </si>
+  <si>
+    <t>ECS Season (n)</t>
+  </si>
+  <si>
+    <t>BetBoom Dacha Season (n)</t>
+  </si>
+  <si>
+    <t>EPICENTER (y)</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Circuit (y)</t>
+  </si>
+  <si>
+    <t>FACEIT Asia League (y)</t>
+  </si>
+  <si>
+    <t>Faceit Europe League (y)</t>
+  </si>
+  <si>
+    <t>Faceit America League (y)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -363,8 +379,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,39 +681,39 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2">
         <v>4</v>
       </c>
     </row>
@@ -704,40 +722,40 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -745,10 +763,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -756,76 +774,76 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -833,10 +851,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -844,87 +862,87 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19">
+      <c r="A19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21">
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -932,65 +950,65 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -998,10 +1016,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -1009,120 +1027,120 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37">
+      <c r="A37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38">
+      <c r="A38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40">
+      <c r="B41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-    </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42">
+      <c r="A42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -1130,10 +1148,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -1141,76 +1159,76 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48">
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50">
+      <c r="A50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1218,32 +1236,32 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53">
+      <c r="A53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1251,441 +1269,441 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56">
+      <c r="A56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="B65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C59">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B71" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B62" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" t="s">
-        <v>90</v>
-      </c>
-      <c r="C68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" t="s">
-        <v>90</v>
-      </c>
-      <c r="C69">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B70" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B82" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B73" t="s">
-        <v>90</v>
-      </c>
-      <c r="C73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B84" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B74" t="s">
-        <v>90</v>
-      </c>
-      <c r="C74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>79</v>
-      </c>
-      <c r="B75" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B85" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B86" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B87" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B78" t="s">
-        <v>90</v>
-      </c>
-      <c r="C78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B88" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B79" t="s">
-        <v>90</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B89" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" t="s">
-        <v>90</v>
-      </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B90" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B91" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B92" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B83" t="s">
-        <v>90</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B93" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" t="s">
-        <v>90</v>
-      </c>
-      <c r="C87">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" t="s">
-        <v>90</v>
-      </c>
-      <c r="C88">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>94</v>
-      </c>
-      <c r="B89" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" t="s">
-        <v>90</v>
-      </c>
-      <c r="C90">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" t="s">
-        <v>90</v>
-      </c>
-      <c r="C91">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" t="s">
-        <v>90</v>
-      </c>
-      <c r="C92">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>99</v>
-      </c>
-      <c r="B94" t="s">
-        <v>90</v>
-      </c>
-      <c r="C94">
+      <c r="B94" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="2">
         <v>5</v>
       </c>
     </row>
